--- a/diseases/d200/2015-2019.xlsx
+++ b/diseases/d200/2015-2019.xlsx
@@ -1009,7 +1009,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1415,7 +1415,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1821,7 +1821,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2227,7 +2227,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2633,7 +2633,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -3039,7 +3039,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3445,7 +3445,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3851,7 +3851,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4257,7 +4257,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4663,7 +4663,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -5069,7 +5069,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5475,7 +5475,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -5881,7 +5881,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6120,7 +6120,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
@@ -6526,7 +6526,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
@@ -6765,7 +6765,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -7171,7 +7171,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7410,7 +7410,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
@@ -7816,7 +7816,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
@@ -8055,7 +8055,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -8461,7 +8461,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8700,7 +8700,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
@@ -9106,7 +9106,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
@@ -9345,7 +9345,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9751,7 +9751,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -9990,7 +9990,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
@@ -10396,7 +10396,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
@@ -10635,7 +10635,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -11041,7 +11041,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -11280,7 +11280,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK52" t="inlineStr">
@@ -11686,7 +11686,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK54" t="inlineStr">
@@ -11925,7 +11925,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -12331,7 +12331,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12570,7 +12570,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK58" t="inlineStr">
@@ -12976,7 +12976,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK60" t="inlineStr">
@@ -13215,7 +13215,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -13621,7 +13621,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -14027,7 +14027,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -14433,7 +14433,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -14839,7 +14839,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -15245,7 +15245,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -15651,7 +15651,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -16057,7 +16057,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -16463,7 +16463,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
@@ -16869,7 +16869,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -17275,7 +17275,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -17681,7 +17681,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -18087,7 +18087,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -18493,7 +18493,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -18732,7 +18732,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK88" t="inlineStr">
@@ -19138,7 +19138,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK90" t="inlineStr">
@@ -19377,7 +19377,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -19783,7 +19783,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -20022,7 +20022,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK94" t="inlineStr">
@@ -20428,7 +20428,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK96" t="inlineStr">
@@ -20667,7 +20667,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -21073,7 +21073,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -21312,7 +21312,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK100" t="inlineStr">
@@ -21718,7 +21718,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK102" t="inlineStr">
@@ -21957,7 +21957,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -22363,7 +22363,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -22602,7 +22602,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK106" t="inlineStr">
@@ -23008,7 +23008,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK108" t="inlineStr">
@@ -23247,7 +23247,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -23653,7 +23653,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -23892,7 +23892,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK112" t="inlineStr">
@@ -24298,7 +24298,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK114" t="inlineStr">
@@ -24537,7 +24537,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -24943,7 +24943,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
@@ -25182,7 +25182,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK118" t="inlineStr">
@@ -25588,7 +25588,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK120" t="inlineStr">
@@ -25827,7 +25827,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
@@ -26233,7 +26233,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -26472,7 +26472,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK124" t="inlineStr">
@@ -26878,7 +26878,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK126" t="inlineStr">
@@ -27117,7 +27117,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
@@ -27523,7 +27523,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
@@ -27762,7 +27762,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK130" t="inlineStr">
@@ -28168,7 +28168,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK132" t="inlineStr">
@@ -28407,7 +28407,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK133" t="inlineStr">
@@ -28813,7 +28813,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -29052,7 +29052,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK136" t="inlineStr">
@@ -29458,7 +29458,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK138" t="inlineStr">
@@ -29697,7 +29697,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
@@ -30103,7 +30103,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK141" t="inlineStr">
@@ -30342,7 +30342,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK142" t="inlineStr">
@@ -30748,7 +30748,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK144" t="inlineStr">
@@ -30987,7 +30987,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK145" t="inlineStr">
@@ -31393,7 +31393,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -31632,7 +31632,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK148" t="inlineStr">
@@ -32038,7 +32038,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK150" t="inlineStr">
@@ -32277,7 +32277,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
@@ -32683,7 +32683,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
@@ -32922,7 +32922,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK154" t="inlineStr">
@@ -33328,7 +33328,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK156" t="inlineStr">
@@ -33567,7 +33567,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK157" t="inlineStr">

--- a/diseases/d200/2015-2019.xlsx
+++ b/diseases/d200/2015-2019.xlsx
@@ -1009,7 +1009,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1415,7 +1415,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1821,7 +1821,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2227,7 +2227,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2633,7 +2633,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -3039,7 +3039,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3445,7 +3445,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3851,7 +3851,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4257,7 +4257,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4663,7 +4663,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -5069,7 +5069,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5475,7 +5475,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -5881,7 +5881,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6120,7 +6120,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
@@ -6526,7 +6526,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
@@ -6765,7 +6765,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -7171,7 +7171,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7410,7 +7410,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
@@ -7816,7 +7816,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
@@ -8055,7 +8055,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -8461,7 +8461,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8700,7 +8700,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
@@ -9106,7 +9106,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
@@ -9345,7 +9345,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9751,7 +9751,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -9990,7 +9990,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
@@ -10396,7 +10396,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
@@ -10635,7 +10635,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -11041,7 +11041,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -11280,7 +11280,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK52" t="inlineStr">
@@ -11686,7 +11686,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK54" t="inlineStr">
@@ -11925,7 +11925,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -12331,7 +12331,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12570,7 +12570,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK58" t="inlineStr">
@@ -12976,7 +12976,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK60" t="inlineStr">
@@ -13215,7 +13215,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -13621,7 +13621,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -14027,7 +14027,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -14433,7 +14433,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -14839,7 +14839,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -15245,7 +15245,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -15651,7 +15651,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -16057,7 +16057,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -16463,7 +16463,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
@@ -16869,7 +16869,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -17275,7 +17275,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -17681,7 +17681,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -18087,7 +18087,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -18493,7 +18493,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -18732,7 +18732,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK88" t="inlineStr">
@@ -19138,7 +19138,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK90" t="inlineStr">
@@ -19377,7 +19377,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -19783,7 +19783,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -20022,7 +20022,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK94" t="inlineStr">
@@ -20428,7 +20428,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK96" t="inlineStr">
@@ -20667,7 +20667,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -21073,7 +21073,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -21312,7 +21312,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK100" t="inlineStr">
@@ -21718,7 +21718,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK102" t="inlineStr">
@@ -21957,7 +21957,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -22363,7 +22363,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -22602,7 +22602,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK106" t="inlineStr">
@@ -23008,7 +23008,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK108" t="inlineStr">
@@ -23247,7 +23247,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -23653,7 +23653,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -23892,7 +23892,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK112" t="inlineStr">
@@ -24298,7 +24298,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK114" t="inlineStr">
@@ -24537,7 +24537,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -24943,7 +24943,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
@@ -25182,7 +25182,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK118" t="inlineStr">
@@ -25588,7 +25588,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK120" t="inlineStr">
@@ -25827,7 +25827,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
@@ -26233,7 +26233,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -26472,7 +26472,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK124" t="inlineStr">
@@ -26878,7 +26878,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK126" t="inlineStr">
@@ -27117,7 +27117,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
@@ -27523,7 +27523,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
@@ -27762,7 +27762,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK130" t="inlineStr">
@@ -28168,7 +28168,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK132" t="inlineStr">
@@ -28407,7 +28407,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK133" t="inlineStr">
@@ -28813,7 +28813,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -29052,7 +29052,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK136" t="inlineStr">
@@ -29458,7 +29458,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK138" t="inlineStr">
@@ -29697,7 +29697,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
@@ -30103,7 +30103,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK141" t="inlineStr">
@@ -30342,7 +30342,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK142" t="inlineStr">
@@ -30748,7 +30748,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK144" t="inlineStr">
@@ -30987,7 +30987,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK145" t="inlineStr">
@@ -31393,7 +31393,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -31632,7 +31632,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK148" t="inlineStr">
@@ -32038,7 +32038,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK150" t="inlineStr">
@@ -32277,7 +32277,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
@@ -32683,7 +32683,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
@@ -32922,7 +32922,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK154" t="inlineStr">
@@ -33328,7 +33328,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK156" t="inlineStr">
@@ -33567,7 +33567,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK157" t="inlineStr">

--- a/diseases/d200/2015-2019.xlsx
+++ b/diseases/d200/2015-2019.xlsx
@@ -765,9 +765,6 @@
       <c r="O2" t="n">
         <v>170</v>
       </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
       <c r="R2" t="n">
         <v>0.08429381507718051</v>
       </c>
@@ -1171,9 +1168,6 @@
       <c r="O4" t="n">
         <v>214</v>
       </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
       <c r="R4" t="n">
         <v>0.106111037803039</v>
       </c>
@@ -1577,9 +1571,6 @@
       <c r="O6" t="n">
         <v>887</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="R6" t="n">
         <v>0.4398153763144653</v>
       </c>
@@ -1983,9 +1974,6 @@
       <c r="O8" t="n">
         <v>769</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="R8" t="n">
         <v>0.3813055517314812</v>
       </c>
@@ -2389,9 +2377,6 @@
       <c r="O10" t="n">
         <v>1338</v>
       </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
       <c r="R10" t="n">
         <v>0.6634419092545148</v>
       </c>
@@ -2795,9 +2780,6 @@
       <c r="O12" t="n">
         <v>814</v>
       </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
       <c r="R12" t="n">
         <v>0.4036186204283819</v>
       </c>
@@ -3201,9 +3183,6 @@
       <c r="O14" t="n">
         <v>390</v>
       </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
       <c r="R14" t="n">
         <v>0.1933799287064729</v>
       </c>
@@ -3607,9 +3586,6 @@
       <c r="O16" t="n">
         <v>2566</v>
       </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
       <c r="R16" t="n">
         <v>1.272340761694384</v>
       </c>
@@ -4013,9 +3989,6 @@
       <c r="O18" t="n">
         <v>4778</v>
       </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
       <c r="R18" t="n">
         <v>2.369152049639815</v>
       </c>
@@ -4419,9 +4392,6 @@
       <c r="O20" t="n">
         <v>5377</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
       <c r="R20" t="n">
         <v>2.666163786294115</v>
       </c>
@@ -4825,9 +4795,6 @@
       <c r="O22" t="n">
         <v>7065</v>
       </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
       <c r="R22" t="n">
         <v>3.503151785413414</v>
       </c>
@@ -5231,9 +5198,6 @@
       <c r="O24" t="n">
         <v>1932</v>
       </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
       <c r="R24" t="n">
         <v>0.9579744160536043</v>
       </c>
@@ -5637,9 +5601,6 @@
       <c r="O26" t="n">
         <v>137</v>
       </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
       <c r="R26" t="n">
         <v>0.06741525036349676</v>
       </c>
@@ -6282,9 +6243,6 @@
       <c r="O29" t="n">
         <v>138</v>
       </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
       <c r="R29" t="n">
         <v>0.06790733248293834</v>
       </c>
@@ -6927,9 +6885,6 @@
       <c r="O32" t="n">
         <v>457</v>
       </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
       <c r="R32" t="n">
         <v>0.2248815285848031</v>
       </c>
@@ -7572,9 +7527,6 @@
       <c r="O35" t="n">
         <v>859</v>
       </c>
-      <c r="Q35" t="n">
-        <v>0</v>
-      </c>
       <c r="R35" t="n">
         <v>0.4226985406003191</v>
       </c>
@@ -8217,9 +8169,6 @@
       <c r="O38" t="n">
         <v>774</v>
       </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
       <c r="R38" t="n">
         <v>0.3808715604477846</v>
       </c>
@@ -8862,9 +8811,6 @@
       <c r="O41" t="n">
         <v>808</v>
       </c>
-      <c r="Q41" t="n">
-        <v>0</v>
-      </c>
       <c r="R41" t="n">
         <v>0.3976023525087984</v>
       </c>
@@ -9507,9 +9453,6 @@
       <c r="O44" t="n">
         <v>312</v>
       </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
       <c r="R44" t="n">
         <v>0.1535296212657736</v>
       </c>
@@ -10152,9 +10095,6 @@
       <c r="O47" t="n">
         <v>2349</v>
       </c>
-      <c r="Q47" t="n">
-        <v>0</v>
-      </c>
       <c r="R47" t="n">
         <v>1.155900898568277</v>
       </c>
@@ -10797,9 +10737,6 @@
       <c r="O50" t="n">
         <v>2171</v>
       </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
       <c r="R50" t="n">
         <v>1.068310281307675</v>
       </c>
@@ -11442,9 +11379,6 @@
       <c r="O53" t="n">
         <v>2879</v>
       </c>
-      <c r="Q53" t="n">
-        <v>0</v>
-      </c>
       <c r="R53" t="n">
         <v>1.416704421872315</v>
       </c>
@@ -12087,9 +12021,6 @@
       <c r="O56" t="n">
         <v>3626</v>
       </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
       <c r="R56" t="n">
         <v>1.784289765095177</v>
       </c>
@@ -12732,9 +12663,6 @@
       <c r="O59" t="n">
         <v>1234</v>
       </c>
-      <c r="Q59" t="n">
-        <v>0</v>
-      </c>
       <c r="R59" t="n">
         <v>0.6072293353909124</v>
       </c>
@@ -13377,9 +13305,6 @@
       <c r="O62" t="n">
         <v>355</v>
       </c>
-      <c r="Q62" t="n">
-        <v>0</v>
-      </c>
       <c r="R62" t="n">
         <v>0.1734216050931629</v>
       </c>
@@ -13783,9 +13708,6 @@
       <c r="O64" t="n">
         <v>416</v>
       </c>
-      <c r="Q64" t="n">
-        <v>0</v>
-      </c>
       <c r="R64" t="n">
         <v>0.2032208104753684</v>
       </c>
@@ -14189,9 +14111,6 @@
       <c r="O66" t="n">
         <v>1884</v>
       </c>
-      <c r="Q66" t="n">
-        <v>0</v>
-      </c>
       <c r="R66" t="n">
         <v>0.9203557859028704</v>
       </c>
@@ -14595,9 +14514,6 @@
       <c r="O68" t="n">
         <v>2138</v>
       </c>
-      <c r="Q68" t="n">
-        <v>0</v>
-      </c>
       <c r="R68" t="n">
         <v>1.044437723068119</v>
       </c>
@@ -15001,9 +14917,6 @@
       <c r="O70" t="n">
         <v>2212</v>
       </c>
-      <c r="Q70" t="n">
-        <v>0</v>
-      </c>
       <c r="R70" t="n">
         <v>1.08058757877768</v>
       </c>
@@ -15407,9 +15320,6 @@
       <c r="O72" t="n">
         <v>760</v>
       </c>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
       <c r="R72" t="n">
         <v>0.3712687883684615</v>
       </c>
@@ -15813,9 +15723,6 @@
       <c r="O74" t="n">
         <v>256</v>
       </c>
-      <c r="Q74" t="n">
-        <v>0</v>
-      </c>
       <c r="R74" t="n">
         <v>0.1250589602925344</v>
       </c>
@@ -16219,9 +16126,6 @@
       <c r="O76" t="n">
         <v>923</v>
       </c>
-      <c r="Q76" t="n">
-        <v>0</v>
-      </c>
       <c r="R76" t="n">
         <v>0.4508961732422236</v>
       </c>
@@ -16625,9 +16529,6 @@
       <c r="O78" t="n">
         <v>945</v>
       </c>
-      <c r="Q78" t="n">
-        <v>0</v>
-      </c>
       <c r="R78" t="n">
         <v>0.4616434276423633</v>
       </c>
@@ -17031,9 +16932,6 @@
       <c r="O80" t="n">
         <v>1393</v>
       </c>
-      <c r="Q80" t="n">
-        <v>0</v>
-      </c>
       <c r="R80" t="n">
         <v>0.6804966081542986</v>
       </c>
@@ -17437,9 +17335,6 @@
       <c r="O82" t="n">
         <v>2923</v>
       </c>
-      <c r="Q82" t="n">
-        <v>0</v>
-      </c>
       <c r="R82" t="n">
         <v>1.427919300527649</v>
       </c>
@@ -17843,9 +17738,6 @@
       <c r="O84" t="n">
         <v>690</v>
       </c>
-      <c r="Q84" t="n">
-        <v>0</v>
-      </c>
       <c r="R84" t="n">
         <v>0.3370729789134717</v>
       </c>
@@ -18249,9 +18141,6 @@
       <c r="O86" t="n">
         <v>42</v>
       </c>
-      <c r="Q86" t="n">
-        <v>0</v>
-      </c>
       <c r="R86" t="n">
         <v>0.02037773919177389</v>
       </c>
@@ -18894,9 +18783,6 @@
       <c r="O89" t="n">
         <v>192</v>
       </c>
-      <c r="Q89" t="n">
-        <v>0</v>
-      </c>
       <c r="R89" t="n">
         <v>0.09315537916239491</v>
       </c>
@@ -19539,9 +19425,6 @@
       <c r="O92" t="n">
         <v>1145</v>
       </c>
-      <c r="Q92" t="n">
-        <v>0</v>
-      </c>
       <c r="R92" t="n">
         <v>0.5555359851090738</v>
       </c>
@@ -20184,9 +20067,6 @@
       <c r="O95" t="n">
         <v>1876</v>
       </c>
-      <c r="Q95" t="n">
-        <v>0</v>
-      </c>
       <c r="R95" t="n">
         <v>0.9102056838992336</v>
       </c>
@@ -20829,9 +20709,6 @@
       <c r="O98" t="n">
         <v>3917</v>
       </c>
-      <c r="Q98" t="n">
-        <v>0</v>
-      </c>
       <c r="R98" t="n">
         <v>1.90046677176615</v>
       </c>
@@ -21474,9 +21351,6 @@
       <c r="O101" t="n">
         <v>5490</v>
       </c>
-      <c r="Q101" t="n">
-        <v>0</v>
-      </c>
       <c r="R101" t="n">
         <v>2.663661622924729</v>
       </c>
@@ -22119,9 +21993,6 @@
       <c r="O104" t="n">
         <v>1783</v>
       </c>
-      <c r="Q104" t="n">
-        <v>0</v>
-      </c>
       <c r="R104" t="n">
         <v>0.8650835471174485</v>
       </c>
@@ -22764,9 +22635,6 @@
       <c r="O107" t="n">
         <v>1338</v>
       </c>
-      <c r="Q107" t="n">
-        <v>0</v>
-      </c>
       <c r="R107" t="n">
         <v>0.6491765485379396</v>
       </c>
@@ -23409,9 +23277,6 @@
       <c r="O110" t="n">
         <v>562</v>
       </c>
-      <c r="Q110" t="n">
-        <v>0</v>
-      </c>
       <c r="R110" t="n">
         <v>0.2726735577565934</v>
       </c>
@@ -24054,9 +23919,6 @@
       <c r="O113" t="n">
         <v>622</v>
       </c>
-      <c r="Q113" t="n">
-        <v>0</v>
-      </c>
       <c r="R113" t="n">
         <v>0.3017846137448418</v>
       </c>
@@ -24699,9 +24561,6 @@
       <c r="O116" t="n">
         <v>828</v>
       </c>
-      <c r="Q116" t="n">
-        <v>0</v>
-      </c>
       <c r="R116" t="n">
         <v>0.4017325726378281</v>
       </c>
@@ -25344,9 +25203,6 @@
       <c r="O119" t="n">
         <v>165</v>
       </c>
-      <c r="Q119" t="n">
-        <v>0</v>
-      </c>
       <c r="R119" t="n">
         <v>0.08005540396768313</v>
       </c>
@@ -25989,9 +25845,6 @@
       <c r="O122" t="n">
         <v>10</v>
       </c>
-      <c r="Q122" t="n">
-        <v>0</v>
-      </c>
       <c r="R122" t="n">
         <v>0.004820311802881235</v>
       </c>
@@ -26634,9 +26487,6 @@
       <c r="O125" t="n">
         <v>113</v>
       </c>
-      <c r="Q125" t="n">
-        <v>0</v>
-      </c>
       <c r="R125" t="n">
         <v>0.05446952337255796</v>
       </c>
@@ -27279,9 +27129,6 @@
       <c r="O128" t="n">
         <v>297</v>
       </c>
-      <c r="Q128" t="n">
-        <v>0</v>
-      </c>
       <c r="R128" t="n">
         <v>0.1431632605455727</v>
       </c>
@@ -27924,9 +27771,6 @@
       <c r="O131" t="n">
         <v>504</v>
       </c>
-      <c r="Q131" t="n">
-        <v>0</v>
-      </c>
       <c r="R131" t="n">
         <v>0.2429437148652142</v>
       </c>
@@ -28569,9 +28413,6 @@
       <c r="O134" t="n">
         <v>463</v>
       </c>
-      <c r="Q134" t="n">
-        <v>0</v>
-      </c>
       <c r="R134" t="n">
         <v>0.2231804364734012</v>
       </c>
@@ -29214,9 +29055,6 @@
       <c r="O137" t="n">
         <v>607</v>
       </c>
-      <c r="Q137" t="n">
-        <v>0</v>
-      </c>
       <c r="R137" t="n">
         <v>0.2925929264348909</v>
       </c>
@@ -29859,9 +29697,6 @@
       <c r="O140" t="n">
         <v>434</v>
       </c>
-      <c r="Q140" t="n">
-        <v>0</v>
-      </c>
       <c r="R140" t="n">
         <v>0.2092015322450456</v>
       </c>
@@ -30504,9 +30339,6 @@
       <c r="O143" t="n">
         <v>893</v>
       </c>
-      <c r="Q143" t="n">
-        <v>0</v>
-      </c>
       <c r="R143" t="n">
         <v>0.4304538439972943</v>
       </c>
@@ -31149,9 +30981,6 @@
       <c r="O146" t="n">
         <v>1086</v>
       </c>
-      <c r="Q146" t="n">
-        <v>0</v>
-      </c>
       <c r="R146" t="n">
         <v>0.5234858617929021</v>
       </c>
@@ -31794,9 +31623,6 @@
       <c r="O149" t="n">
         <v>516</v>
       </c>
-      <c r="Q149" t="n">
-        <v>0</v>
-      </c>
       <c r="R149" t="n">
         <v>0.2487280890286717</v>
       </c>
@@ -32439,9 +32265,6 @@
       <c r="O152" t="n">
         <v>854</v>
       </c>
-      <c r="Q152" t="n">
-        <v>0</v>
-      </c>
       <c r="R152" t="n">
         <v>0.4116546279660575</v>
       </c>
@@ -33083,9 +32906,6 @@
       </c>
       <c r="O155" t="n">
         <v>654</v>
-      </c>
-      <c r="Q155" t="n">
-        <v>0</v>
       </c>
       <c r="R155" t="n">
         <v>0.3152483919084328</v>

--- a/diseases/d200/2015-2019.xlsx
+++ b/diseases/d200/2015-2019.xlsx
@@ -1006,7 +1006,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1812,7 +1812,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2215,7 +2215,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3827,7 +3827,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4230,7 +4230,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4633,7 +4633,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -5036,7 +5036,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5439,7 +5439,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -5842,7 +5842,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6081,7 +6081,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
@@ -6484,7 +6484,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
@@ -6723,7 +6723,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -7126,7 +7126,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7365,7 +7365,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
@@ -7768,7 +7768,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
@@ -8007,7 +8007,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -8410,7 +8410,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8649,7 +8649,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
@@ -9052,7 +9052,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
@@ -9291,7 +9291,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9694,7 +9694,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -9933,7 +9933,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
@@ -10336,7 +10336,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
@@ -10575,7 +10575,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -10978,7 +10978,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -11217,7 +11217,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK52" t="inlineStr">
@@ -11620,7 +11620,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK54" t="inlineStr">
@@ -11859,7 +11859,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -12262,7 +12262,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12501,7 +12501,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK58" t="inlineStr">
@@ -12904,7 +12904,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK60" t="inlineStr">
@@ -13143,7 +13143,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -13546,7 +13546,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -13949,7 +13949,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -14352,7 +14352,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -14755,7 +14755,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -15158,7 +15158,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -15561,7 +15561,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -15964,7 +15964,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -16367,7 +16367,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
@@ -16770,7 +16770,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -17173,7 +17173,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -17576,7 +17576,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -17979,7 +17979,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -18382,7 +18382,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -18621,7 +18621,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK88" t="inlineStr">
@@ -19024,7 +19024,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK90" t="inlineStr">
@@ -19263,7 +19263,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -19666,7 +19666,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -19905,7 +19905,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK94" t="inlineStr">
@@ -20308,7 +20308,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK96" t="inlineStr">
@@ -20547,7 +20547,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -20950,7 +20950,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -21189,7 +21189,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK100" t="inlineStr">
@@ -21592,7 +21592,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK102" t="inlineStr">
@@ -21831,7 +21831,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -22234,7 +22234,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -22473,7 +22473,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK106" t="inlineStr">
@@ -22876,7 +22876,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK108" t="inlineStr">
@@ -23115,7 +23115,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -23518,7 +23518,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -23757,7 +23757,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK112" t="inlineStr">
@@ -24160,7 +24160,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK114" t="inlineStr">
@@ -24399,7 +24399,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -24802,7 +24802,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
@@ -25041,7 +25041,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK118" t="inlineStr">
@@ -25444,7 +25444,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK120" t="inlineStr">
@@ -25683,7 +25683,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
@@ -26086,7 +26086,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -26325,7 +26325,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK124" t="inlineStr">
@@ -26728,7 +26728,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK126" t="inlineStr">
@@ -26967,7 +26967,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
@@ -27370,7 +27370,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
@@ -27609,7 +27609,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK130" t="inlineStr">
@@ -28012,7 +28012,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK132" t="inlineStr">
@@ -28251,7 +28251,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK133" t="inlineStr">
@@ -28654,7 +28654,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -28893,7 +28893,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK136" t="inlineStr">
@@ -29296,7 +29296,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK138" t="inlineStr">
@@ -29535,7 +29535,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
@@ -29938,7 +29938,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK141" t="inlineStr">
@@ -30177,7 +30177,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK142" t="inlineStr">
@@ -30580,7 +30580,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK144" t="inlineStr">
@@ -30819,7 +30819,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK145" t="inlineStr">
@@ -31222,7 +31222,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -31461,7 +31461,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK148" t="inlineStr">
@@ -31864,7 +31864,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK150" t="inlineStr">
@@ -32103,7 +32103,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
@@ -32506,7 +32506,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
@@ -32745,7 +32745,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK154" t="inlineStr">
@@ -33148,7 +33148,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK156" t="inlineStr">
@@ -33387,7 +33387,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK157" t="inlineStr">

--- a/diseases/d200/2015-2019.xlsx
+++ b/diseases/d200/2015-2019.xlsx
@@ -1006,7 +1006,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1812,7 +1812,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2215,7 +2215,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3827,7 +3827,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4230,7 +4230,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4633,7 +4633,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -5036,7 +5036,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5439,7 +5439,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -5842,7 +5842,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6081,7 +6081,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
@@ -6484,7 +6484,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
@@ -6723,7 +6723,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -7126,7 +7126,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7365,7 +7365,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
@@ -7768,7 +7768,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
@@ -8007,7 +8007,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -8410,7 +8410,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8649,7 +8649,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
@@ -9052,7 +9052,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
@@ -9291,7 +9291,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9694,7 +9694,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -9933,7 +9933,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
@@ -10336,7 +10336,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
@@ -10575,7 +10575,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -10978,7 +10978,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -11217,7 +11217,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK52" t="inlineStr">
@@ -11620,7 +11620,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK54" t="inlineStr">
@@ -11859,7 +11859,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -12262,7 +12262,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12501,7 +12501,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK58" t="inlineStr">
@@ -12904,7 +12904,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK60" t="inlineStr">
@@ -13143,7 +13143,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -13546,7 +13546,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -13949,7 +13949,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -14352,7 +14352,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -14755,7 +14755,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -15158,7 +15158,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -15561,7 +15561,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -15964,7 +15964,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -16367,7 +16367,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
@@ -16770,7 +16770,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -17173,7 +17173,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -17576,7 +17576,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -17979,7 +17979,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -18382,7 +18382,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -18621,7 +18621,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK88" t="inlineStr">
@@ -19024,7 +19024,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK90" t="inlineStr">
@@ -19263,7 +19263,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -19666,7 +19666,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -19905,7 +19905,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK94" t="inlineStr">
@@ -20308,7 +20308,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK96" t="inlineStr">
@@ -20547,7 +20547,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -20950,7 +20950,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -21189,7 +21189,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK100" t="inlineStr">
@@ -21592,7 +21592,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK102" t="inlineStr">
@@ -21831,7 +21831,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -22234,7 +22234,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -22473,7 +22473,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK106" t="inlineStr">
@@ -22876,7 +22876,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK108" t="inlineStr">
@@ -23115,7 +23115,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -23518,7 +23518,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -23757,7 +23757,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK112" t="inlineStr">
@@ -24160,7 +24160,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK114" t="inlineStr">
@@ -24399,7 +24399,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -24802,7 +24802,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
@@ -25041,7 +25041,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK118" t="inlineStr">
@@ -25444,7 +25444,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK120" t="inlineStr">
@@ -25683,7 +25683,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
@@ -26086,7 +26086,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -26325,7 +26325,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK124" t="inlineStr">
@@ -26728,7 +26728,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK126" t="inlineStr">
@@ -26967,7 +26967,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
@@ -27370,7 +27370,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
@@ -27609,7 +27609,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK130" t="inlineStr">
@@ -28012,7 +28012,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK132" t="inlineStr">
@@ -28251,7 +28251,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK133" t="inlineStr">
@@ -28654,7 +28654,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -28893,7 +28893,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK136" t="inlineStr">
@@ -29296,7 +29296,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK138" t="inlineStr">
@@ -29535,7 +29535,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
@@ -29938,7 +29938,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK141" t="inlineStr">
@@ -30177,7 +30177,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK142" t="inlineStr">
@@ -30580,7 +30580,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK144" t="inlineStr">
@@ -30819,7 +30819,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK145" t="inlineStr">
@@ -31222,7 +31222,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -31461,7 +31461,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK148" t="inlineStr">
@@ -31864,7 +31864,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK150" t="inlineStr">
@@ -32103,7 +32103,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
@@ -32506,7 +32506,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
@@ -32745,7 +32745,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK154" t="inlineStr">
@@ -33148,7 +33148,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK156" t="inlineStr">
@@ -33387,7 +33387,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK157" t="inlineStr">

--- a/diseases/d200/2015-2019.xlsx
+++ b/diseases/d200/2015-2019.xlsx
@@ -1006,7 +1006,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1812,7 +1812,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2215,7 +2215,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3827,7 +3827,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4230,7 +4230,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4633,7 +4633,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -5036,7 +5036,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5439,7 +5439,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -5842,7 +5842,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6081,7 +6081,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
@@ -6484,7 +6484,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
@@ -6723,7 +6723,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -7126,7 +7126,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7365,7 +7365,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
@@ -7768,7 +7768,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
@@ -8007,7 +8007,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -8410,7 +8410,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8649,7 +8649,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
@@ -9052,7 +9052,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
@@ -9291,7 +9291,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9694,7 +9694,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -9933,7 +9933,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
@@ -10336,7 +10336,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
@@ -10575,7 +10575,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -10978,7 +10978,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -11217,7 +11217,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK52" t="inlineStr">
@@ -11620,7 +11620,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK54" t="inlineStr">
@@ -11859,7 +11859,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -12262,7 +12262,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12501,7 +12501,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK58" t="inlineStr">
@@ -12904,7 +12904,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK60" t="inlineStr">
@@ -13143,7 +13143,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -13546,7 +13546,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -13949,7 +13949,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -14352,7 +14352,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -14755,7 +14755,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -15158,7 +15158,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -15561,7 +15561,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -15964,7 +15964,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -16367,7 +16367,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
@@ -16770,7 +16770,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -17173,7 +17173,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -17576,7 +17576,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -17979,7 +17979,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -18382,7 +18382,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -18621,7 +18621,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK88" t="inlineStr">
@@ -19024,7 +19024,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK90" t="inlineStr">
@@ -19263,7 +19263,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -19666,7 +19666,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -19905,7 +19905,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK94" t="inlineStr">
@@ -20308,7 +20308,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK96" t="inlineStr">
@@ -20547,7 +20547,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -20950,7 +20950,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -21189,7 +21189,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK100" t="inlineStr">
@@ -21592,7 +21592,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK102" t="inlineStr">
@@ -21831,7 +21831,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -22234,7 +22234,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -22473,7 +22473,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK106" t="inlineStr">
@@ -22876,7 +22876,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK108" t="inlineStr">
@@ -23115,7 +23115,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -23518,7 +23518,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -23757,7 +23757,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK112" t="inlineStr">
@@ -24160,7 +24160,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK114" t="inlineStr">
@@ -24399,7 +24399,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -24802,7 +24802,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
@@ -25041,7 +25041,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK118" t="inlineStr">
@@ -25444,7 +25444,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK120" t="inlineStr">
@@ -25683,7 +25683,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
@@ -26086,7 +26086,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -26325,7 +26325,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK124" t="inlineStr">
@@ -26728,7 +26728,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK126" t="inlineStr">
@@ -26967,7 +26967,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
@@ -27370,7 +27370,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
@@ -27609,7 +27609,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK130" t="inlineStr">
@@ -28012,7 +28012,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK132" t="inlineStr">
@@ -28251,7 +28251,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK133" t="inlineStr">
@@ -28654,7 +28654,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -28893,7 +28893,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK136" t="inlineStr">
@@ -29296,7 +29296,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK138" t="inlineStr">
@@ -29535,7 +29535,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
@@ -29938,7 +29938,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK141" t="inlineStr">
@@ -30177,7 +30177,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK142" t="inlineStr">
@@ -30580,7 +30580,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK144" t="inlineStr">
@@ -30819,7 +30819,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK145" t="inlineStr">
@@ -31222,7 +31222,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -31461,7 +31461,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK148" t="inlineStr">
@@ -31864,7 +31864,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK150" t="inlineStr">
@@ -32103,7 +32103,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
@@ -32506,7 +32506,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
@@ -32745,7 +32745,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK154" t="inlineStr">
@@ -33148,7 +33148,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK156" t="inlineStr">
@@ -33387,7 +33387,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK157" t="inlineStr">

--- a/diseases/d200/2015-2019.xlsx
+++ b/diseases/d200/2015-2019.xlsx
@@ -1006,7 +1006,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1812,7 +1812,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2215,7 +2215,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3827,7 +3827,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4230,7 +4230,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4633,7 +4633,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -5036,7 +5036,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5439,7 +5439,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -5842,7 +5842,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6081,7 +6081,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
@@ -6484,7 +6484,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
@@ -6723,7 +6723,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -7126,7 +7126,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7365,7 +7365,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
@@ -7768,7 +7768,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
@@ -8007,7 +8007,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -8410,7 +8410,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8649,7 +8649,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
@@ -9052,7 +9052,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
@@ -9291,7 +9291,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9694,7 +9694,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -9933,7 +9933,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
@@ -10336,7 +10336,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
@@ -10575,7 +10575,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -10978,7 +10978,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -11217,7 +11217,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK52" t="inlineStr">
@@ -11620,7 +11620,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK54" t="inlineStr">
@@ -11859,7 +11859,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -12262,7 +12262,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12501,7 +12501,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK58" t="inlineStr">
@@ -12904,7 +12904,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK60" t="inlineStr">
@@ -13143,7 +13143,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -13546,7 +13546,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -13949,7 +13949,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -14352,7 +14352,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -14755,7 +14755,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -15158,7 +15158,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -15561,7 +15561,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -15964,7 +15964,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -16367,7 +16367,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
@@ -16770,7 +16770,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -17173,7 +17173,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -17576,7 +17576,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -17979,7 +17979,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -18382,7 +18382,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -18621,7 +18621,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK88" t="inlineStr">
@@ -19024,7 +19024,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK90" t="inlineStr">
@@ -19263,7 +19263,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -19666,7 +19666,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -19905,7 +19905,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK94" t="inlineStr">
@@ -20308,7 +20308,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK96" t="inlineStr">
@@ -20547,7 +20547,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -20950,7 +20950,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -21189,7 +21189,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK100" t="inlineStr">
@@ -21592,7 +21592,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK102" t="inlineStr">
@@ -21831,7 +21831,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -22234,7 +22234,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -22473,7 +22473,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK106" t="inlineStr">
@@ -22876,7 +22876,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK108" t="inlineStr">
@@ -23115,7 +23115,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -23518,7 +23518,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -23757,7 +23757,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK112" t="inlineStr">
@@ -24160,7 +24160,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK114" t="inlineStr">
@@ -24399,7 +24399,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -24802,7 +24802,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
@@ -25041,7 +25041,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK118" t="inlineStr">
@@ -25444,7 +25444,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK120" t="inlineStr">
@@ -25683,7 +25683,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
@@ -26086,7 +26086,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -26325,7 +26325,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK124" t="inlineStr">
@@ -26728,7 +26728,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK126" t="inlineStr">
@@ -26967,7 +26967,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
@@ -27370,7 +27370,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
@@ -27609,7 +27609,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK130" t="inlineStr">
@@ -28012,7 +28012,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK132" t="inlineStr">
@@ -28251,7 +28251,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK133" t="inlineStr">
@@ -28654,7 +28654,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -28893,7 +28893,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK136" t="inlineStr">
@@ -29296,7 +29296,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK138" t="inlineStr">
@@ -29535,7 +29535,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
@@ -29938,7 +29938,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK141" t="inlineStr">
@@ -30177,7 +30177,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK142" t="inlineStr">
@@ -30580,7 +30580,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK144" t="inlineStr">
@@ -30819,7 +30819,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK145" t="inlineStr">
@@ -31222,7 +31222,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -31461,7 +31461,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK148" t="inlineStr">
@@ -31864,7 +31864,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK150" t="inlineStr">
@@ -32103,7 +32103,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
@@ -32506,7 +32506,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
@@ -32745,7 +32745,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK154" t="inlineStr">
@@ -33148,7 +33148,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK156" t="inlineStr">
@@ -33387,7 +33387,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK157" t="inlineStr">
